--- a/MCCC/Data/catalog.xlsx
+++ b/MCCC/Data/catalog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0acdb00829658b64/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0acdb00829658b64/Documents/Crochet/MCCC/MCCC/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="8_{C2233ACA-21A4-415D-A3EB-C25FF75F4FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8890A05-4DCA-4503-9DD1-A3954A3ED790}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="8_{C2233ACA-21A4-415D-A3EB-C25FF75F4FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8932DB1-795C-4D9F-BC5B-14904C3F3DB0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D99117FC-4EF0-44A2-9BD9-65554D1BB8E8}"/>
   </bookViews>
@@ -53,301 +53,301 @@
     <t>Applesaurus</t>
   </si>
   <si>
-    <t>applesaurus</t>
-  </si>
-  <si>
     <t>Baby Ballerina Slippers</t>
   </si>
   <si>
-    <t>babyBallerinaSlippers</t>
-  </si>
-  <si>
-    <t>babyDino</t>
-  </si>
-  <si>
     <t>Baby Dino</t>
   </si>
   <si>
     <t>Baby Sleep Sack</t>
   </si>
   <si>
-    <t>babySack</t>
-  </si>
-  <si>
     <t>Baby Clothing Set</t>
   </si>
   <si>
-    <t>babySet</t>
-  </si>
-  <si>
     <t>Butterfly Blanket</t>
   </si>
   <si>
-    <t>butterflyRainbowBlanket</t>
-  </si>
-  <si>
     <t>Camera Purse</t>
   </si>
   <si>
-    <t>cameraPurse</t>
-  </si>
-  <si>
     <t>Flowers</t>
   </si>
   <si>
-    <t>daffodilNarcussis</t>
-  </si>
-  <si>
     <t>Daisies</t>
   </si>
   <si>
-    <t>daisies</t>
-  </si>
-  <si>
     <t>Dinosaur Dog Sweater</t>
   </si>
   <si>
-    <t>dogDinoSweater</t>
-  </si>
-  <si>
     <t>Dinosaur Pillow</t>
   </si>
   <si>
-    <t>dinoPillow</t>
-  </si>
-  <si>
     <t>Dog Pouch</t>
   </si>
   <si>
-    <t>dogPouch</t>
-  </si>
-  <si>
     <t>Easter Wreath</t>
   </si>
   <si>
-    <t>easterWreath</t>
-  </si>
-  <si>
     <t>Emotional Dumplings</t>
   </si>
   <si>
-    <t>emotionalDumplings</t>
-  </si>
-  <si>
     <t>Forest Dragon</t>
   </si>
   <si>
-    <t>giantDragon</t>
-  </si>
-  <si>
     <t>Giant Jellyfish</t>
   </si>
   <si>
-    <t>giantJellyfish</t>
-  </si>
-  <si>
     <t>Giraffe Keychain</t>
   </si>
   <si>
-    <t>giraffeKeychain</t>
-  </si>
-  <si>
     <t>Granny Stitch Bucket Hat</t>
   </si>
   <si>
-    <t>grannyStitchBucketHat1</t>
-  </si>
-  <si>
     <t>Strawberry Bucket Hat</t>
   </si>
   <si>
-    <t>grannyStitchBucketHat2</t>
-  </si>
-  <si>
     <t>Halter Top</t>
   </si>
   <si>
-    <t>halterTop</t>
-  </si>
-  <si>
     <t>Hanging Vine</t>
   </si>
   <si>
-    <t>hangingFlowers</t>
-  </si>
-  <si>
     <t>Hanging Name Sign</t>
   </si>
   <si>
-    <t>hangingName</t>
-  </si>
-  <si>
     <t>Honeycomb Habitat</t>
   </si>
   <si>
-    <t>honeyComb</t>
-  </si>
-  <si>
     <t>Hooded Cowl</t>
   </si>
   <si>
-    <t>hoodedCowl</t>
-  </si>
-  <si>
     <t>Ice Cream Turtle</t>
   </si>
   <si>
-    <t>iceCreamTurtle</t>
-  </si>
-  <si>
     <t>It's 420 Somewhere</t>
   </si>
   <si>
-    <t>its420Blanket</t>
-  </si>
-  <si>
     <t>Floor-Length Dress</t>
   </si>
   <si>
-    <t>laceDress</t>
-  </si>
-  <si>
     <t>Cover-Up Sweater</t>
   </si>
   <si>
-    <t>laceSweater</t>
-  </si>
-  <si>
     <t>Lap Blanket</t>
   </si>
   <si>
-    <t>lapBlanket</t>
-  </si>
-  <si>
     <t>Laptop Case</t>
   </si>
   <si>
-    <t>laptopCase</t>
-  </si>
-  <si>
     <t>Lavendar</t>
   </si>
   <si>
-    <t>lavendar</t>
-  </si>
-  <si>
     <t>Little Gnome</t>
   </si>
   <si>
-    <t>littleGnome</t>
-  </si>
-  <si>
     <t>Loonette (Big Comfy Couch)</t>
   </si>
   <si>
-    <t>loonette</t>
-  </si>
-  <si>
     <t>Mom and Me Bandanas</t>
   </si>
   <si>
-    <t>matchingBandanas</t>
-  </si>
-  <si>
     <t>Matching Sweaters</t>
   </si>
   <si>
     <t>90/sweater</t>
   </si>
   <si>
-    <t>matchingSweaters</t>
-  </si>
-  <si>
     <t>Molly Doll</t>
   </si>
   <si>
-    <t>mollyDoll</t>
-  </si>
-  <si>
     <t>Penguin Keychain</t>
   </si>
   <si>
-    <t>penguinKeychain</t>
-  </si>
-  <si>
     <t>Personalized Blanket</t>
   </si>
   <si>
-    <t>personalizedBlanket</t>
-  </si>
-  <si>
     <t>Pocket Turtle</t>
   </si>
   <si>
-    <t>pocketTurtle</t>
-  </si>
-  <si>
     <t>Pokeball</t>
   </si>
   <si>
-    <t>pokeball</t>
-  </si>
-  <si>
     <t>Pokemon (Charmander, Squirtle, Bulbasaur, Snorlax)</t>
   </si>
   <si>
     <t>30/each</t>
   </si>
   <si>
-    <t>pokemon</t>
-  </si>
-  <si>
     <t>Potion Bottle Dice Holders</t>
   </si>
   <si>
-    <t>potionBottle</t>
-  </si>
-  <si>
     <t>Over-The-Shoulder Purse</t>
   </si>
   <si>
-    <t>shoulderPurse</t>
-  </si>
-  <si>
     <t>Sleeping Kirby</t>
   </si>
   <si>
-    <t>sleepingKirby</t>
-  </si>
-  <si>
     <t>Jellyfish</t>
   </si>
   <si>
-    <t>smallJellyfish</t>
-  </si>
-  <si>
     <t>Starfish</t>
   </si>
   <si>
-    <t>starfish</t>
-  </si>
-  <si>
     <t>Tank Top Dress</t>
   </si>
   <si>
-    <t>tankDress</t>
-  </si>
-  <si>
     <t>Tic Tac Toe</t>
   </si>
   <si>
-    <t>ticTacToe</t>
-  </si>
-  <si>
     <t>T-Rex</t>
   </si>
   <si>
-    <t>tRex</t>
+    <t>applesaurus.JPG</t>
+  </si>
+  <si>
+    <t>babyBallerinaSlippers.JPG</t>
+  </si>
+  <si>
+    <t>babyDino.JPG</t>
+  </si>
+  <si>
+    <t>babySack.JPG</t>
+  </si>
+  <si>
+    <t>babySet.JPG</t>
+  </si>
+  <si>
+    <t>butterflyRainbowBlanket.JPG</t>
+  </si>
+  <si>
+    <t>cameraPurse.JPG</t>
+  </si>
+  <si>
+    <t>daffodilNarcussis.JPG</t>
+  </si>
+  <si>
+    <t>daisies.JPG</t>
+  </si>
+  <si>
+    <t>tRex.JPG</t>
+  </si>
+  <si>
+    <t>ticTacToe.JPG</t>
+  </si>
+  <si>
+    <t>tankDress.JPG</t>
+  </si>
+  <si>
+    <t>starfish.JPG</t>
+  </si>
+  <si>
+    <t>smallJellyfish.JPG</t>
+  </si>
+  <si>
+    <t>sleepingKirby.JPG</t>
+  </si>
+  <si>
+    <t>shoulderPurse.JPG</t>
+  </si>
+  <si>
+    <t>potionBottle.JPG</t>
+  </si>
+  <si>
+    <t>pokemon.JPG</t>
+  </si>
+  <si>
+    <t>pokeball.JPG</t>
+  </si>
+  <si>
+    <t>pocketTurtle.JPG</t>
+  </si>
+  <si>
+    <t>personalizedBlanket.JPG</t>
+  </si>
+  <si>
+    <t>penguinKeychain.JPG</t>
+  </si>
+  <si>
+    <t>mollyDoll.JPG</t>
+  </si>
+  <si>
+    <t>matchingSweaters.JPG</t>
+  </si>
+  <si>
+    <t>matchingBandanas.JPG</t>
+  </si>
+  <si>
+    <t>loonette.JPG</t>
+  </si>
+  <si>
+    <t>littleGnome.JPG</t>
+  </si>
+  <si>
+    <t>lavendar.JPG</t>
+  </si>
+  <si>
+    <t>laptopCase.JPG</t>
+  </si>
+  <si>
+    <t>lapBlanket.JPG</t>
+  </si>
+  <si>
+    <t>laceSweater.JPG</t>
+  </si>
+  <si>
+    <t>laceDress.JPG</t>
+  </si>
+  <si>
+    <t>its420Blanket.JPG</t>
+  </si>
+  <si>
+    <t>iceCreamTurtle.JPG</t>
+  </si>
+  <si>
+    <t>hoodedCowl.JPG</t>
+  </si>
+  <si>
+    <t>honeyComb.JPG</t>
+  </si>
+  <si>
+    <t>hangingName.JPG</t>
+  </si>
+  <si>
+    <t>hangingFlowers.JPG</t>
+  </si>
+  <si>
+    <t>halterTop.JPG</t>
+  </si>
+  <si>
+    <t>grannyStitchBucketHat2.JPG</t>
+  </si>
+  <si>
+    <t>grannyStitchBucketHat1.JPG</t>
+  </si>
+  <si>
+    <t>giraffeKeychain.JPG</t>
+  </si>
+  <si>
+    <t>dogDinoSweater.JPG</t>
+  </si>
+  <si>
+    <t>dinoPillow.JPG</t>
+  </si>
+  <si>
+    <t>dogPouch.JPG</t>
+  </si>
+  <si>
+    <t>emotionalDumplings.JPG</t>
+  </si>
+  <si>
+    <t>easterWreath.JPG</t>
+  </si>
+  <si>
+    <t>giantDragon.JPG</t>
+  </si>
+  <si>
+    <t>giantJellyfish.JPG</t>
   </si>
 </sst>
 </file>
@@ -750,535 +750,535 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B11">
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>1000</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B20">
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B22">
         <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="B23">
         <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B24">
         <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B25">
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B27">
         <v>150</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B28">
         <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="B29">
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="B30">
         <v>150</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="B31">
         <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B32">
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="B33">
         <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="B34">
         <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="B35">
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="B37">
         <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="B38">
         <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="B39">
         <v>200</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B40">
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="B41">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="C42" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="B43">
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="B44">
         <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="B45">
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="B46">
         <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="B47">
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="B48">
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="B49">
         <v>30</v>
       </c>
       <c r="C49" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="B50">
         <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/MCCC/Data/catalog.xlsx
+++ b/MCCC/Data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0acdb00829658b64/Documents/Crochet/MCCC/MCCC/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="8_{C2233ACA-21A4-415D-A3EB-C25FF75F4FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8932DB1-795C-4D9F-BC5B-14904C3F3DB0}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="8_{C2233ACA-21A4-415D-A3EB-C25FF75F4FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C694E9BC-7A5B-4B5C-8A8B-8006D8BDCCC8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D99117FC-4EF0-44A2-9BD9-65554D1BB8E8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="118">
   <si>
     <t>Name</t>
   </si>
@@ -176,9 +176,6 @@
     <t>Pokemon (Charmander, Squirtle, Bulbasaur, Snorlax)</t>
   </si>
   <si>
-    <t>30/each</t>
-  </si>
-  <si>
     <t>Potion Bottle Dice Holders</t>
   </si>
   <si>
@@ -348,6 +345,54 @@
   </si>
   <si>
     <t>giantJellyfish.JPG</t>
+  </si>
+  <si>
+    <t>5/each</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>30-60/each</t>
+  </si>
+  <si>
+    <t>1ft in height by 1ft in length</t>
+  </si>
+  <si>
+    <t>Made for a 10lbs Goldendoodle puppy</t>
+  </si>
+  <si>
+    <t>Fits 2-month-old baby</t>
+  </si>
+  <si>
+    <t>Can be made in sizes Newborn, 3-6m, 6-12m</t>
+  </si>
+  <si>
+    <t>Made for a 24lbs Goldendoodle dog</t>
+  </si>
+  <si>
+    <t>Small enough to fit in your pocket! (~2in wide)</t>
+  </si>
+  <si>
+    <t>8.5ft long from nose to tail (sitting on a double bed)</t>
+  </si>
+  <si>
+    <t>1ft long</t>
+  </si>
+  <si>
+    <t>One size fits all</t>
+  </si>
+  <si>
+    <t>Picture shows 2 medium tops</t>
+  </si>
+  <si>
+    <t>Made for a gecko, the honeycomb is around 4in wide and 7in tall</t>
+  </si>
+  <si>
+    <t>Adult size</t>
+  </si>
+  <si>
+    <t>5ft by 5.5ft</t>
   </si>
 </sst>
 </file>
@@ -723,15 +768,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B7C9D55-FAC3-40FD-B87F-807CEE1EC2A8}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" customWidth="1"/>
+    <col min="4" max="4" width="40.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -741,41 +787,47 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="D3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -783,10 +835,13 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="D5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -794,10 +849,10 @@
         <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -805,10 +860,10 @@
         <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -816,32 +871,32 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -849,54 +904,63 @@
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="D13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B15">
-        <v>5</v>
+      <c r="B15" t="s">
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -904,10 +968,13 @@
         <v>1000</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -915,10 +982,13 @@
         <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -926,10 +996,10 @@
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -937,10 +1007,13 @@
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -948,10 +1021,13 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="D20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -959,10 +1035,13 @@
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="D21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -970,10 +1049,10 @@
         <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -981,10 +1060,10 @@
         <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -992,10 +1071,13 @@
         <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="D24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1003,10 +1085,13 @@
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="D25" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1014,10 +1099,10 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1025,21 +1110,24 @@
         <v>150</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="D27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
       <c r="B28">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -1047,10 +1135,10 @@
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1058,10 +1146,10 @@
         <v>150</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1069,18 +1157,18 @@
         <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1091,7 +1179,7 @@
         <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1102,7 +1190,7 @@
         <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1113,7 +1201,7 @@
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1124,7 +1212,7 @@
         <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1135,7 +1223,7 @@
         <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1146,7 +1234,7 @@
         <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1157,7 +1245,7 @@
         <v>200</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1165,10 +1253,10 @@
         <v>42</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1179,7 +1267,7 @@
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1187,98 +1275,101 @@
         <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="C42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48">
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49">
         <v>30</v>
       </c>
       <c r="C49" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="D50" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/MCCC/Data/catalog.xlsx
+++ b/MCCC/Data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0acdb00829658b64/Documents/Crochet/MCCC/MCCC/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="243" documentId="8_{C2233ACA-21A4-415D-A3EB-C25FF75F4FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C694E9BC-7A5B-4B5C-8A8B-8006D8BDCCC8}"/>
+  <xr:revisionPtr revIDLastSave="289" documentId="8_{C2233ACA-21A4-415D-A3EB-C25FF75F4FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D20D495-AF5B-4743-8BCD-49150A9E33DA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D99117FC-4EF0-44A2-9BD9-65554D1BB8E8}"/>
+    <workbookView minimized="1" xWindow="16860" yWindow="2820" windowWidth="12285" windowHeight="7725" xr2:uid="{D99117FC-4EF0-44A2-9BD9-65554D1BB8E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="144">
   <si>
     <t>Name</t>
   </si>
@@ -393,6 +393,84 @@
   </si>
   <si>
     <t>5ft by 5.5ft</t>
+  </si>
+  <si>
+    <t>3.5ft long</t>
+  </si>
+  <si>
+    <t>4in tall</t>
+  </si>
+  <si>
+    <t>16in by 16in</t>
+  </si>
+  <si>
+    <t>5in by 7in</t>
+  </si>
+  <si>
+    <t>6in tall</t>
+  </si>
+  <si>
+    <t>4ft long by 2ft wide</t>
+  </si>
+  <si>
+    <t>Medium fit</t>
+  </si>
+  <si>
+    <t>5in tall</t>
+  </si>
+  <si>
+    <t>Each letter is about 4in wide</t>
+  </si>
+  <si>
+    <t>20in tall</t>
+  </si>
+  <si>
+    <t>1ft tall</t>
+  </si>
+  <si>
+    <t>2in wide</t>
+  </si>
+  <si>
+    <t>8in tall</t>
+  </si>
+  <si>
+    <t>1ft wide</t>
+  </si>
+  <si>
+    <t>4in wide</t>
+  </si>
+  <si>
+    <t>4in wide by 6in tall</t>
+  </si>
+  <si>
+    <t>7in wide</t>
+  </si>
+  <si>
+    <t>6in by 1ft</t>
+  </si>
+  <si>
+    <t>Medium to XL fit</t>
+  </si>
+  <si>
+    <t>Fits 17in laptop</t>
+  </si>
+  <si>
+    <t>16in tall by 8in wide</t>
+  </si>
+  <si>
+    <t>2in wide by 1ft tall</t>
+  </si>
+  <si>
+    <t>1in wide by 1ft tall</t>
+  </si>
+  <si>
+    <t>3.5in wide by 1ft tall</t>
+  </si>
+  <si>
+    <t>Fits 1-year-old</t>
+  </si>
+  <si>
+    <t>18in square</t>
   </si>
 </sst>
 </file>
@@ -801,6 +879,9 @@
       <c r="C2" t="s">
         <v>53</v>
       </c>
+      <c r="D2" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -826,6 +907,9 @@
       <c r="C4" t="s">
         <v>55</v>
       </c>
+      <c r="D4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -851,6 +935,9 @@
       <c r="C6" t="s">
         <v>57</v>
       </c>
+      <c r="D6" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -862,16 +949,22 @@
       <c r="C7" t="s">
         <v>58</v>
       </c>
+      <c r="D7" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>59</v>
+      </c>
+      <c r="D8" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -884,6 +977,9 @@
       <c r="C9" t="s">
         <v>60</v>
       </c>
+      <c r="D9" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -895,13 +991,16 @@
       <c r="C10" t="s">
         <v>61</v>
       </c>
+      <c r="D10" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>95</v>
@@ -920,6 +1019,9 @@
       <c r="C12" t="s">
         <v>96</v>
       </c>
+      <c r="D12" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -940,10 +1042,13 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
         <v>99</v>
+      </c>
+      <c r="D14" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -993,10 +1098,13 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
         <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1051,6 +1159,9 @@
       <c r="C22" t="s">
         <v>90</v>
       </c>
+      <c r="D22" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -1062,13 +1173,16 @@
       <c r="C23" t="s">
         <v>89</v>
       </c>
+      <c r="D23" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
       <c r="B24">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
         <v>88</v>
@@ -1101,6 +1215,9 @@
       <c r="C26" t="s">
         <v>86</v>
       </c>
+      <c r="D26" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -1126,6 +1243,9 @@
       <c r="C28" t="s">
         <v>84</v>
       </c>
+      <c r="D28" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -1137,6 +1257,9 @@
       <c r="C29" t="s">
         <v>83</v>
       </c>
+      <c r="D29" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -1148,16 +1271,22 @@
       <c r="C30" t="s">
         <v>82</v>
       </c>
+      <c r="D30" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
       <c r="B31">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
         <v>81</v>
+      </c>
+      <c r="D31" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1170,30 +1299,39 @@
       <c r="C32" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
       <c r="B33">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C34" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1203,8 +1341,11 @@
       <c r="C35" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1214,19 +1355,25 @@
       <c r="C36" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
       <c r="B37">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -1236,8 +1383,11 @@
       <c r="C38" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -1247,8 +1397,11 @@
       <c r="C39" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -1258,19 +1411,25 @@
       <c r="C40" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C41" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1280,8 +1439,11 @@
       <c r="C42" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1291,8 +1453,11 @@
       <c r="C43" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -1302,8 +1467,11 @@
       <c r="C44" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -1313,8 +1481,11 @@
       <c r="C45" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -1324,8 +1495,11 @@
       <c r="C46" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -1335,8 +1509,11 @@
       <c r="C47" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -1345,6 +1522,9 @@
       </c>
       <c r="C48" t="s">
         <v>64</v>
+      </c>
+      <c r="D48" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1356,6 +1536,9 @@
       </c>
       <c r="C49" t="s">
         <v>63</v>
+      </c>
+      <c r="D49" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">

--- a/MCCC/Data/catalog.xlsx
+++ b/MCCC/Data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0acdb00829658b64/Documents/Crochet/MCCC/MCCC/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="289" documentId="8_{C2233ACA-21A4-415D-A3EB-C25FF75F4FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D20D495-AF5B-4743-8BCD-49150A9E33DA}"/>
+  <xr:revisionPtr revIDLastSave="344" documentId="8_{C2233ACA-21A4-415D-A3EB-C25FF75F4FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7685203C-2469-4ACB-A596-0454C3121EB6}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="16860" yWindow="2820" windowWidth="12285" windowHeight="7725" xr2:uid="{D99117FC-4EF0-44A2-9BD9-65554D1BB8E8}"/>
+    <workbookView minimized="1" xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11295" xr2:uid="{D99117FC-4EF0-44A2-9BD9-65554D1BB8E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="146">
   <si>
     <t>Name</t>
   </si>
@@ -471,6 +471,12 @@
   </si>
   <si>
     <t>18in square</t>
+  </si>
+  <si>
+    <t>Time to Make (hrs)</t>
+  </si>
+  <si>
+    <t>2.5 months</t>
   </si>
 </sst>
 </file>
@@ -523,10 +529,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -846,16 +848,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B7C9D55-FAC3-40FD-B87F-807CEE1EC2A8}">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
     <col min="3" max="3" width="26.42578125" customWidth="1"/>
-    <col min="4" max="4" width="40.28515625" customWidth="1"/>
+    <col min="4" max="4" width="61.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -868,8 +871,11 @@
       <c r="D1" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -882,8 +888,11 @@
       <c r="D2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -896,8 +905,11 @@
       <c r="D3" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -910,8 +922,11 @@
       <c r="D4" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -924,8 +939,11 @@
       <c r="D5" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -938,8 +956,11 @@
       <c r="D6" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -952,8 +973,11 @@
       <c r="D7" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -966,8 +990,11 @@
       <c r="D8" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -980,8 +1007,11 @@
       <c r="D9" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -994,8 +1024,11 @@
       <c r="D10" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1008,8 +1041,11 @@
       <c r="D11" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1022,8 +1058,11 @@
       <c r="D12" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1036,8 +1075,11 @@
       <c r="D13" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1050,8 +1092,11 @@
       <c r="D14" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1064,8 +1109,11 @@
       <c r="D15" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1078,8 +1126,11 @@
       <c r="D16" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1092,8 +1143,11 @@
       <c r="D17" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1106,8 +1160,11 @@
       <c r="D18" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1120,8 +1177,11 @@
       <c r="D19" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1134,8 +1194,11 @@
       <c r="D20" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1148,8 +1211,11 @@
       <c r="D21" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1162,8 +1228,11 @@
       <c r="D22" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1176,8 +1245,11 @@
       <c r="D23" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -1190,8 +1262,11 @@
       <c r="D24" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1204,8 +1279,11 @@
       <c r="D25" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1218,8 +1296,11 @@
       <c r="D26" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1232,8 +1313,11 @@
       <c r="D27" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1246,8 +1330,11 @@
       <c r="D28" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -1260,8 +1347,11 @@
       <c r="D29" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1274,8 +1364,11 @@
       <c r="D30" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1288,8 +1381,11 @@
       <c r="D31" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1302,8 +1398,11 @@
       <c r="D32" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1316,8 +1415,11 @@
       <c r="D33" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1330,8 +1432,11 @@
       <c r="D34" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1344,8 +1449,11 @@
       <c r="D35" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1358,8 +1466,11 @@
       <c r="D36" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -1372,8 +1483,11 @@
       <c r="D37" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -1386,8 +1500,11 @@
       <c r="D38" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -1400,8 +1517,11 @@
       <c r="D39" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -1414,8 +1534,11 @@
       <c r="D40" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -1428,8 +1551,11 @@
       <c r="D41" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1442,8 +1568,11 @@
       <c r="D42" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1456,8 +1585,11 @@
       <c r="D43" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -1470,8 +1602,11 @@
       <c r="D44" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -1484,8 +1619,11 @@
       <c r="D45" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -1498,8 +1636,11 @@
       <c r="D46" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -1512,8 +1653,11 @@
       <c r="D47" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -1526,8 +1670,11 @@
       <c r="D48" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1540,8 +1687,11 @@
       <c r="D49" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -1553,6 +1703,9 @@
       </c>
       <c r="D50" t="s">
         <v>105</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/MCCC/Data/catalog.xlsx
+++ b/MCCC/Data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0acdb00829658b64/Documents/Crochet/MCCC/MCCC/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="344" documentId="8_{C2233ACA-21A4-415D-A3EB-C25FF75F4FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7685203C-2469-4ACB-A596-0454C3121EB6}"/>
+  <xr:revisionPtr revIDLastSave="474" documentId="8_{C2233ACA-21A4-415D-A3EB-C25FF75F4FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{101555CF-985E-4712-B1EC-6B11AAEE1AC8}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11295" xr2:uid="{D99117FC-4EF0-44A2-9BD9-65554D1BB8E8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D99117FC-4EF0-44A2-9BD9-65554D1BB8E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="155">
   <si>
     <t>Name</t>
   </si>
@@ -477,13 +477,52 @@
   </si>
   <si>
     <t>2.5 months</t>
+  </si>
+  <si>
+    <t>75 days</t>
+  </si>
+  <si>
+    <t>5 hours</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>Labour</t>
+  </si>
+  <si>
+    <t>Labour Rate</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>Total Discount</t>
+  </si>
+  <si>
+    <t>Difference</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,12 +531,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -509,16 +566,69 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -529,6 +639,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -848,17 +962,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B7C9D55-FAC3-40FD-B87F-807CEE1EC2A8}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
     <col min="3" max="3" width="26.42578125" customWidth="1"/>
     <col min="4" max="4" width="61.28515625" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="23" style="4" customWidth="1"/>
+    <col min="7" max="7" width="20" style="7" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" style="8" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -871,11 +991,38 @@
       <c r="D1" t="s">
         <v>103</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="6" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" t="s">
+        <v>154</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="O1" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -888,16 +1035,36 @@
       <c r="D2" t="s">
         <v>122</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="4">
+        <f>E2*$O$1</f>
+        <v>40</v>
+      </c>
+      <c r="H2" s="5">
+        <f>F2+G2</f>
+        <v>40</v>
+      </c>
+      <c r="J2" s="4">
+        <f>IF(I2=0,0,(H2*I2))</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="3">
+        <f>H2-J2</f>
+        <v>40</v>
+      </c>
+      <c r="L2" s="2">
+        <f>B2-K2</f>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>54</v>
@@ -905,11 +1072,37 @@
       <c r="D3" t="s">
         <v>108</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="6">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="4">
+        <f>E3*$O$1</f>
+        <v>5</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <f t="shared" ref="H3:H50" si="0">F3+G3</f>
+        <v>6</v>
+      </c>
+      <c r="I3" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="J3" s="4">
+        <f>IF(I3=0,0,(H3*I3))</f>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="K3" s="3">
+        <f>H3-J3</f>
+        <v>4.8</v>
+      </c>
+      <c r="L3" s="2">
+        <f t="shared" ref="L3:L50" si="1">B3-K3</f>
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -922,11 +1115,34 @@
       <c r="D4" t="s">
         <v>122</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="4">
+        <f>E4*$O$1</f>
+        <v>20</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <f t="shared" ref="J4:J51" si="2">IF(I4=0,0,(H4*I4))</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <f t="shared" ref="K4:K50" si="3">H4-J4</f>
+        <v>20</v>
+      </c>
+      <c r="L4" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -939,11 +1155,34 @@
       <c r="D5" t="s">
         <v>107</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="6">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="4">
+        <f>E5*$O$1</f>
+        <v>30</v>
+      </c>
+      <c r="H5" s="5">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="L5" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -956,11 +1195,34 @@
       <c r="D6" t="s">
         <v>142</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="4">
+        <f>E6*$O$1</f>
+        <v>80</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="L6" s="2">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -973,11 +1235,31 @@
       <c r="D7" t="s">
         <v>143</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="4">
+        <f>E7*$O$1</f>
+        <v>200</v>
+      </c>
+      <c r="H7" s="5">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="J7" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="3">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="L7" s="2">
+        <f t="shared" si="1"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -990,11 +1272,31 @@
       <c r="D8" t="s">
         <v>121</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="4">
+        <f>E8*$O$1</f>
+        <v>20</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J8" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="L8" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1007,11 +1309,31 @@
       <c r="D9" t="s">
         <v>141</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="6">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="4">
+        <f>E9*$O$1</f>
+        <v>3</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J9" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="L9" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1024,16 +1346,36 @@
       <c r="D10" t="s">
         <v>139</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="6">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="4">
+        <f>E10*$O$1</f>
+        <v>5</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J10" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="L10" s="2">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
         <v>95</v>
@@ -1041,11 +1383,31 @@
       <c r="D11" t="s">
         <v>109</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="4">
+        <f>E11*$O$1</f>
+        <v>60</v>
+      </c>
+      <c r="H11" s="5">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="J11" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="L11" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1058,16 +1420,36 @@
       <c r="D12" t="s">
         <v>120</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="4">
+        <f>E12*$O$1</f>
+        <v>40</v>
+      </c>
+      <c r="H12" s="5">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="J12" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="L12" s="2">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
         <v>97</v>
@@ -1075,11 +1457,31 @@
       <c r="D13" t="s">
         <v>106</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="4">
+        <f>E13*$O$1</f>
+        <v>40</v>
+      </c>
+      <c r="H13" s="5">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="J13" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="L13" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1092,11 +1494,31 @@
       <c r="D14" t="s">
         <v>138</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="6">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="4">
+        <f>E14*$O$1</f>
+        <v>30</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="J14" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="L14" s="2">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1109,11 +1531,31 @@
       <c r="D15" t="s">
         <v>110</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="6">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="4">
+        <f>E15*$O$1</f>
+        <v>3</v>
+      </c>
+      <c r="H15" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J15" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="L15" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1126,11 +1568,43 @@
       <c r="D16" t="s">
         <v>111</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="6">
+        <v>375</v>
+      </c>
+      <c r="F16" s="4">
+        <f>E16*$O$1</f>
+        <v>7500</v>
+      </c>
+      <c r="H16" s="5">
+        <f t="shared" si="0"/>
+        <v>7500</v>
+      </c>
+      <c r="I16" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="J16" s="4">
+        <f t="shared" si="2"/>
+        <v>6000</v>
+      </c>
+      <c r="K16" s="3">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="L16" s="2">
+        <f t="shared" si="1"/>
+        <v>-500</v>
+      </c>
+      <c r="M16" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="N16" t="s">
+        <v>146</v>
+      </c>
+      <c r="O16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1143,11 +1617,31 @@
       <c r="D17" t="s">
         <v>112</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="6">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="4">
+        <f>E17*$O$1</f>
+        <v>240</v>
+      </c>
+      <c r="H17" s="5">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="J17" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+      <c r="L17" s="2">
+        <f t="shared" si="1"/>
+        <v>-165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1160,11 +1654,31 @@
       <c r="D18" t="s">
         <v>119</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="6">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="4">
+        <f>E18*$O$1</f>
+        <v>30</v>
+      </c>
+      <c r="H18" s="5">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="J18" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="L18" s="2">
+        <f t="shared" si="1"/>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1177,11 +1691,31 @@
       <c r="D19" t="s">
         <v>113</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="4">
+        <f>E19*$O$1</f>
+        <v>20</v>
+      </c>
+      <c r="H19" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J19" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="L19" s="2">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1194,11 +1728,31 @@
       <c r="D20" t="s">
         <v>113</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="4">
+        <f>E20*$O$1</f>
+        <v>20</v>
+      </c>
+      <c r="H20" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J20" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="L20" s="2">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1211,11 +1765,31 @@
       <c r="D21" t="s">
         <v>114</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="6">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="4">
+        <f>E21*$O$1</f>
+        <v>30</v>
+      </c>
+      <c r="H21" s="5">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="J21" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="L21" s="2">
+        <f t="shared" si="1"/>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1228,11 +1802,31 @@
       <c r="D22" t="s">
         <v>118</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="6">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="4">
+        <f>E22*$O$1</f>
+        <v>240</v>
+      </c>
+      <c r="H22" s="5">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="J22" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+      <c r="L22" s="2">
+        <f t="shared" si="1"/>
+        <v>-180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1245,16 +1839,36 @@
       <c r="D23" t="s">
         <v>126</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="4">
+        <f>E23*$O$1</f>
+        <v>80</v>
+      </c>
+      <c r="H23" s="5">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J23" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="L23" s="2">
+        <f t="shared" si="1"/>
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
       <c r="B24">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
         <v>88</v>
@@ -1262,16 +1876,36 @@
       <c r="D24" t="s">
         <v>115</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="4">
+        <f>E24*$O$1</f>
+        <v>100</v>
+      </c>
+      <c r="H24" s="5">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J24" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="L24" s="2">
+        <f t="shared" si="1"/>
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
       <c r="B25">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
         <v>87</v>
@@ -1279,16 +1913,36 @@
       <c r="D25" t="s">
         <v>116</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="4">
+        <f>E25*$O$1</f>
+        <v>40</v>
+      </c>
+      <c r="H25" s="5">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="J25" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="L25" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
       <c r="B26">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
         <v>86</v>
@@ -1296,11 +1950,31 @@
       <c r="D26" t="s">
         <v>125</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="4">
+        <f>E26*$O$1</f>
+        <v>40</v>
+      </c>
+      <c r="H26" s="5">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="J26" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="L26" s="2">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1313,11 +1987,31 @@
       <c r="D27" t="s">
         <v>117</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="6">
         <v>30</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="4">
+        <f>E27*$O$1</f>
+        <v>600</v>
+      </c>
+      <c r="H27" s="5">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+      <c r="J27" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <f t="shared" si="3"/>
+        <v>600</v>
+      </c>
+      <c r="L27" s="2">
+        <f t="shared" si="1"/>
+        <v>-450</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1330,11 +2024,31 @@
       <c r="D28" t="s">
         <v>124</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="4">
+        <f>E28*$O$1</f>
+        <v>200</v>
+      </c>
+      <c r="H28" s="5">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="J28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="L28" s="2">
+        <f t="shared" si="1"/>
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -1347,11 +2061,31 @@
       <c r="D29" t="s">
         <v>124</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="6">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="4">
+        <f>E29*$O$1</f>
+        <v>50</v>
+      </c>
+      <c r="H29" s="5">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="J29" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="L29" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1364,11 +2098,31 @@
       <c r="D30" t="s">
         <v>123</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="6">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="4">
+        <f>E30*$O$1</f>
+        <v>30</v>
+      </c>
+      <c r="H30" s="5">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="J30" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="L30" s="2">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1381,11 +2135,31 @@
       <c r="D31" t="s">
         <v>137</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="4">
+        <f>E31*$O$1</f>
+        <v>100</v>
+      </c>
+      <c r="H31" s="5">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J31" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="3">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="L31" s="2">
+        <f t="shared" si="1"/>
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1398,11 +2172,31 @@
       <c r="D32" t="s">
         <v>140</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="6">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="4">
+        <f>E32*$O$1</f>
+        <v>10</v>
+      </c>
+      <c r="H32" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="J32" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="L32" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1415,79 +2209,179 @@
       <c r="D33" t="s">
         <v>119</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="4">
+        <f>E33*$O$1</f>
+        <v>20</v>
+      </c>
+      <c r="H33" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J33" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="L33" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34">
+        <v>10</v>
+      </c>
+      <c r="C34" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" s="6">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4">
+        <f>E34*$O$1</f>
+        <v>20</v>
+      </c>
+      <c r="H34" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J34" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="L34" s="2">
+        <f t="shared" si="1"/>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" s="6">
+        <v>8</v>
+      </c>
+      <c r="F35" s="4">
+        <f>E35*$O$1</f>
+        <v>160</v>
+      </c>
+      <c r="H35" s="5">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="J35" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
+        <f t="shared" si="3"/>
+        <v>160</v>
+      </c>
+      <c r="L35" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36">
+        <v>65</v>
+      </c>
+      <c r="C36" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36" s="6">
+        <v>12</v>
+      </c>
+      <c r="F36" s="4">
+        <f>E36*$O$1</f>
+        <v>240</v>
+      </c>
+      <c r="H36" s="5">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="J36" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+      <c r="L36" s="2">
+        <f t="shared" si="1"/>
+        <v>-175</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>35</v>
       </c>
-      <c r="B34">
-        <v>65</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B37">
+        <v>80</v>
+      </c>
+      <c r="C37" t="s">
         <v>78</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D37" t="s">
         <v>127</v>
       </c>
-      <c r="E34">
+      <c r="E37" s="6">
         <v>16</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35">
-        <v>10</v>
-      </c>
-      <c r="C35" t="s">
-        <v>77</v>
-      </c>
-      <c r="D35" t="s">
-        <v>113</v>
-      </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36" t="s">
-        <v>136</v>
-      </c>
-      <c r="E36">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37">
-        <v>50</v>
-      </c>
-      <c r="C37" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37" t="s">
-        <v>128</v>
-      </c>
-      <c r="E37">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37" s="4">
+        <f>E37*$O$1</f>
+        <v>320</v>
+      </c>
+      <c r="H37" s="5">
+        <f t="shared" si="0"/>
+        <v>320</v>
+      </c>
+      <c r="J37" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="3">
+        <f t="shared" si="3"/>
+        <v>320</v>
+      </c>
+      <c r="L37" s="2">
+        <f t="shared" si="1"/>
+        <v>-240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -1500,11 +2394,31 @@
       <c r="D38" t="s">
         <v>119</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="6">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38" s="4">
+        <f>E38*$O$1</f>
+        <v>30</v>
+      </c>
+      <c r="H38" s="5">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="J38" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="L38" s="2">
+        <f t="shared" si="1"/>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -1517,11 +2431,31 @@
       <c r="D39" t="s">
         <v>123</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="6">
         <v>50</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39" s="4">
+        <f>E39*$O$1</f>
+        <v>1000</v>
+      </c>
+      <c r="H39" s="5">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="J39" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="3">
+        <f t="shared" si="3"/>
+        <v>1000</v>
+      </c>
+      <c r="L39" s="2">
+        <f t="shared" si="1"/>
+        <v>-800</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -1534,11 +2468,34 @@
       <c r="D40" t="s">
         <v>129</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="6">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40" s="4">
+        <f>E40*$O$1</f>
+        <v>3</v>
+      </c>
+      <c r="G40" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="H40" s="5">
+        <f t="shared" si="0"/>
+        <v>3.5</v>
+      </c>
+      <c r="J40" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="3">
+        <f t="shared" si="3"/>
+        <v>3.5</v>
+      </c>
+      <c r="L40" s="2">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -1551,11 +2508,31 @@
       <c r="D41" t="s">
         <v>129</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="6">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41" s="4">
+        <f>E41*$O$1</f>
+        <v>10</v>
+      </c>
+      <c r="H41" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="J41" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="L41" s="2">
+        <f t="shared" si="1"/>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1568,11 +2545,31 @@
       <c r="D42" t="s">
         <v>122</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42" s="4">
+        <f>E42*$O$1</f>
+        <v>40</v>
+      </c>
+      <c r="H42" s="5">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="J42" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="L42" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1585,11 +2582,31 @@
       <c r="D43" t="s">
         <v>130</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43" s="4">
+        <f>E43*$O$1</f>
+        <v>20</v>
+      </c>
+      <c r="H43" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J43" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="L43" s="2">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -1602,16 +2619,36 @@
       <c r="D44" t="s">
         <v>131</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44" s="4">
+        <f>E44*$O$1</f>
+        <v>60</v>
+      </c>
+      <c r="H44" s="5">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="J44" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="L44" s="2">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
       <c r="B45">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C45" t="s">
         <v>67</v>
@@ -1619,16 +2656,36 @@
       <c r="D45" t="s">
         <v>132</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45" s="4">
+        <f>E45*$O$1</f>
+        <v>40</v>
+      </c>
+      <c r="H45" s="5">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="J45" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="L45" s="2">
+        <f t="shared" si="1"/>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
       <c r="B46">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C46" t="s">
         <v>66</v>
@@ -1636,11 +2693,31 @@
       <c r="D46" t="s">
         <v>133</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46" s="4">
+        <f>E46*$O$1</f>
+        <v>20</v>
+      </c>
+      <c r="H46" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J46" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="L46" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -1653,16 +2730,36 @@
       <c r="D47" t="s">
         <v>134</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47" s="4">
+        <f>E47*$O$1</f>
+        <v>40</v>
+      </c>
+      <c r="H47" s="5">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="J47" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="L47" s="2">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
       <c r="B48">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="C48" t="s">
         <v>64</v>
@@ -1670,11 +2767,31 @@
       <c r="D48" t="s">
         <v>124</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="6">
         <v>7</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48" s="4">
+        <f>E48*$O$1</f>
+        <v>140</v>
+      </c>
+      <c r="H48" s="5">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+      <c r="J48" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="3">
+        <f t="shared" si="3"/>
+        <v>140</v>
+      </c>
+      <c r="L48" s="2">
+        <f t="shared" si="1"/>
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1687,11 +2804,31 @@
       <c r="D49" t="s">
         <v>135</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49" s="4">
+        <f>E49*$O$1</f>
+        <v>40</v>
+      </c>
+      <c r="H49" s="5">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="J49" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="L49" s="2">
+        <f t="shared" si="1"/>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -1704,11 +2841,39 @@
       <c r="D50" t="s">
         <v>105</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="6">
         <v>5</v>
       </c>
+      <c r="F50" s="4">
+        <f>E50*$O$1</f>
+        <v>100</v>
+      </c>
+      <c r="H50" s="5">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="3">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="L50" s="2">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="L2:L50">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>